--- a/medical_data/boundary_ablation/results/kvasir/kvasir_boundary_ablation.xlsx
+++ b/medical_data/boundary_ablation/results/kvasir/kvasir_boundary_ablation.xlsx
@@ -463,35 +463,35 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9217</v>
+        <v>0.9164</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9062</v>
+        <v>0.9108000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9879</v>
+        <v>0.9845</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9911</v>
+        <v>0.9918</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.905</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9008</v>
+        <v>0.9165</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9819</v>
+        <v>0.9816</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9873</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="4">
@@ -501,54 +501,54 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9069</v>
+        <v>0.9187</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.9124</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9837</v>
+        <v>0.9851</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9886</v>
+        <v>0.9925</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9119</v>
+        <v>0.9091</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9194</v>
+        <v>0.9015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9805</v>
+        <v>0.9835</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9915</v>
+        <v>0.9922</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.9087</v>
+        <v>0.914</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9038</v>
+        <v>0.908</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9828</v>
+        <v>0.9841</v>
       </c>
       <c r="E6" t="n">
-        <v>0.99</v>
+        <v>0.9923</v>
       </c>
     </row>
   </sheetData>
@@ -562,7 +562,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D101"/>
+  <dimension ref="A1:D284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -597,10 +597,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.678874</v>
+        <v>1.65589</v>
       </c>
       <c r="D2" t="n">
-        <v>0.812057</v>
+        <v>0.820478</v>
       </c>
     </row>
     <row r="3">
@@ -613,10 +613,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.946509</v>
+        <v>0.97844</v>
       </c>
       <c r="D3" t="n">
-        <v>0.839287</v>
+        <v>0.83133</v>
       </c>
     </row>
     <row r="4">
@@ -629,10 +629,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.730595</v>
+        <v>0.730815</v>
       </c>
       <c r="D4" t="n">
-        <v>0.85254</v>
+        <v>0.890661</v>
       </c>
     </row>
     <row r="5">
@@ -645,10 +645,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.661991</v>
+        <v>0.647699</v>
       </c>
       <c r="D5" t="n">
-        <v>0.873454</v>
+        <v>0.867488</v>
       </c>
     </row>
     <row r="6">
@@ -661,10 +661,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5772929999999999</v>
+        <v>0.577633</v>
       </c>
       <c r="D6" t="n">
-        <v>0.860706</v>
+        <v>0.888317</v>
       </c>
     </row>
     <row r="7">
@@ -677,10 +677,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.541054</v>
+        <v>0.5197079999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8993</v>
+        <v>0.887445</v>
       </c>
     </row>
     <row r="8">
@@ -693,10 +693,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.504026</v>
+        <v>0.577062</v>
       </c>
       <c r="D8" t="n">
-        <v>0.898072</v>
+        <v>0.890472</v>
       </c>
     </row>
     <row r="9">
@@ -709,10 +709,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.404724</v>
+        <v>0.437973</v>
       </c>
       <c r="D9" t="n">
-        <v>0.901931</v>
+        <v>0.908698</v>
       </c>
     </row>
     <row r="10">
@@ -725,10 +725,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.361066</v>
+        <v>0.370816</v>
       </c>
       <c r="D10" t="n">
-        <v>0.904249</v>
+        <v>0.890666</v>
       </c>
     </row>
     <row r="11">
@@ -741,10 +741,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.3488</v>
+        <v>0.442475</v>
       </c>
       <c r="D11" t="n">
-        <v>0.913884</v>
+        <v>0.90263</v>
       </c>
     </row>
     <row r="12">
@@ -757,10 +757,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.305845</v>
+        <v>0.368919</v>
       </c>
       <c r="D12" t="n">
-        <v>0.916643</v>
+        <v>0.873323</v>
       </c>
     </row>
     <row r="13">
@@ -773,10 +773,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.280251</v>
+        <v>0.362846</v>
       </c>
       <c r="D13" t="n">
-        <v>0.922829</v>
+        <v>0.887068</v>
       </c>
     </row>
     <row r="14">
@@ -789,10 +789,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.277994</v>
+        <v>0.328802</v>
       </c>
       <c r="D14" t="n">
-        <v>0.915714</v>
+        <v>0.8902910000000001</v>
       </c>
     </row>
     <row r="15">
@@ -805,10 +805,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.271615</v>
+        <v>0.294369</v>
       </c>
       <c r="D15" t="n">
-        <v>0.918279</v>
+        <v>0.902363</v>
       </c>
     </row>
     <row r="16">
@@ -821,10 +821,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.244129</v>
+        <v>0.31823</v>
       </c>
       <c r="D16" t="n">
-        <v>0.923935</v>
+        <v>0.8986499999999999</v>
       </c>
     </row>
     <row r="17">
@@ -837,10 +837,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>0.245349</v>
+        <v>0.300243</v>
       </c>
       <c r="D17" t="n">
-        <v>0.92252</v>
+        <v>0.904686</v>
       </c>
     </row>
     <row r="18">
@@ -853,10 +853,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.227115</v>
+        <v>0.272833</v>
       </c>
       <c r="D18" t="n">
-        <v>0.924085</v>
+        <v>0.9110009999999999</v>
       </c>
     </row>
     <row r="19">
@@ -869,10 +869,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.214786</v>
+        <v>0.285113</v>
       </c>
       <c r="D19" t="n">
-        <v>0.927409</v>
+        <v>0.915479</v>
       </c>
     </row>
     <row r="20">
@@ -885,10 +885,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.225397</v>
+        <v>0.28885</v>
       </c>
       <c r="D20" t="n">
-        <v>0.924561</v>
+        <v>0.909125</v>
       </c>
     </row>
     <row r="21">
@@ -901,1290 +901,4218 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.219067</v>
+        <v>0.241311</v>
       </c>
       <c r="D21" t="n">
-        <v>0.922732</v>
+        <v>0.920334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>1.802969</v>
+        <v>0.216009</v>
       </c>
       <c r="D22" t="n">
-        <v>0.805732</v>
+        <v>0.909925</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>1.108424</v>
+        <v>0.23435</v>
       </c>
       <c r="D23" t="n">
-        <v>0.847725</v>
+        <v>0.9115799999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.866967</v>
+        <v>0.223279</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8686700000000001</v>
+        <v>0.915263</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7452569999999999</v>
+        <v>0.209977</v>
       </c>
       <c r="D25" t="n">
-        <v>0.891108</v>
+        <v>0.908687</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.665455</v>
+        <v>0.211502</v>
       </c>
       <c r="D26" t="n">
-        <v>0.898275</v>
+        <v>0.925403</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>0.578501</v>
+        <v>0.184626</v>
       </c>
       <c r="D27" t="n">
-        <v>0.88763</v>
+        <v>0.925782</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.536599</v>
+        <v>0.185265</v>
       </c>
       <c r="D28" t="n">
-        <v>0.902621</v>
+        <v>0.904924</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.447648</v>
+        <v>0.200434</v>
       </c>
       <c r="D29" t="n">
-        <v>0.900258</v>
+        <v>0.902713</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.433364</v>
+        <v>0.246336</v>
       </c>
       <c r="D30" t="n">
-        <v>0.900718</v>
+        <v>0.904782</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.3999</v>
+        <v>0.197803</v>
       </c>
       <c r="D31" t="n">
-        <v>0.912879</v>
+        <v>0.915238</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>0.361897</v>
+        <v>0.178136</v>
       </c>
       <c r="D32" t="n">
-        <v>0.908465</v>
+        <v>0.913629</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>0.352765</v>
+        <v>0.16722</v>
       </c>
       <c r="D33" t="n">
-        <v>0.898215</v>
+        <v>0.922666</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.307571</v>
+        <v>0.165594</v>
       </c>
       <c r="D34" t="n">
-        <v>0.912932</v>
+        <v>0.926169</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.304644</v>
+        <v>0.16305</v>
       </c>
       <c r="D35" t="n">
-        <v>0.908133</v>
+        <v>0.917019</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>0.276092</v>
+        <v>0.162383</v>
       </c>
       <c r="D36" t="n">
-        <v>0.911918</v>
+        <v>0.916259</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>0.267009</v>
+        <v>0.153531</v>
       </c>
       <c r="D37" t="n">
-        <v>0.913994</v>
+        <v>0.927249</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>0.268353</v>
+        <v>0.148937</v>
       </c>
       <c r="D38" t="n">
-        <v>0.9176530000000001</v>
+        <v>0.921543</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>0.234889</v>
+        <v>0.148572</v>
       </c>
       <c r="D39" t="n">
-        <v>0.91855</v>
+        <v>0.92096</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>0.251316</v>
+        <v>0.138861</v>
       </c>
       <c r="D40" t="n">
-        <v>0.913354</v>
+        <v>0.910694</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>PLWCE+Dice                  (α=13.026) [baseline]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>0.254568</v>
+        <v>0.142373</v>
       </c>
       <c r="D41" t="n">
-        <v>0.915353</v>
+        <v>0.92132</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>1.705228</v>
+        <v>0.138775</v>
       </c>
       <c r="D42" t="n">
-        <v>0.807717</v>
+        <v>0.9098889999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>0.9123289999999999</v>
+        <v>0.146027</v>
       </c>
       <c r="D43" t="n">
-        <v>0.846063</v>
+        <v>0.913474</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3</v>
+        <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>0.653925</v>
+        <v>0.145249</v>
       </c>
       <c r="D44" t="n">
-        <v>0.879983</v>
+        <v>0.910375</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>0.582909</v>
+        <v>0.138314</v>
       </c>
       <c r="D45" t="n">
-        <v>0.881123</v>
+        <v>0.919784</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>0.444723</v>
+        <v>0.132189</v>
       </c>
       <c r="D46" t="n">
-        <v>0.871186</v>
+        <v>0.9184600000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>0.385005</v>
+        <v>0.133494</v>
       </c>
       <c r="D47" t="n">
-        <v>0.885506</v>
+        <v>0.911095</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>0.296654</v>
+        <v>0.122241</v>
       </c>
       <c r="D48" t="n">
-        <v>0.888279</v>
+        <v>0.918031</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>0.248097</v>
+        <v>0.118743</v>
       </c>
       <c r="D49" t="n">
-        <v>0.900869</v>
+        <v>0.917104</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>0.181685</v>
+        <v>0.118379</v>
       </c>
       <c r="D50" t="n">
-        <v>0.903189</v>
+        <v>0.918257</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>0.158102</v>
+        <v>0.120379</v>
       </c>
       <c r="D51" t="n">
-        <v>0.8998</v>
+        <v>0.91403</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>CE+Dice                     [baseline]</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C52" t="n">
-        <v>0.122862</v>
+        <v>0.115295</v>
       </c>
       <c r="D52" t="n">
-        <v>0.905541</v>
+        <v>0.915326</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C53" t="n">
-        <v>0.118699</v>
+        <v>1.838034</v>
       </c>
       <c r="D53" t="n">
-        <v>0.907025</v>
+        <v>0.766601</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
-        <v>0.109332</v>
+        <v>1.090172</v>
       </c>
       <c r="D54" t="n">
-        <v>0.908876</v>
+        <v>0.8334819999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="C55" t="n">
-        <v>0.09510299999999999</v>
+        <v>0.9071709999999999</v>
       </c>
       <c r="D55" t="n">
-        <v>0.899315</v>
+        <v>0.871942</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C56" t="n">
-        <v>0.082856</v>
+        <v>0.750598</v>
       </c>
       <c r="D56" t="n">
-        <v>0.907639</v>
+        <v>0.875351</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C57" t="n">
-        <v>0.08748599999999999</v>
+        <v>0.640374</v>
       </c>
       <c r="D57" t="n">
-        <v>0.912575</v>
+        <v>0.888718</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="C58" t="n">
-        <v>0.088085</v>
+        <v>0.577645</v>
       </c>
       <c r="D58" t="n">
-        <v>0.9095760000000001</v>
+        <v>0.884537</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="C59" t="n">
-        <v>0.08022700000000001</v>
+        <v>0.552999</v>
       </c>
       <c r="D59" t="n">
-        <v>0.910894</v>
+        <v>0.892357</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="C60" t="n">
-        <v>0.07700700000000001</v>
+        <v>0.504953</v>
       </c>
       <c r="D60" t="n">
-        <v>0.911294</v>
+        <v>0.87022</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CE+Dice+BL                  [literature]</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C61" t="n">
-        <v>0.081374</v>
+        <v>0.428078</v>
       </c>
       <c r="D61" t="n">
-        <v>0.91287</v>
+        <v>0.901883</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C62" t="n">
-        <v>1.832524</v>
+        <v>0.449939</v>
       </c>
       <c r="D62" t="n">
-        <v>0.7621559999999999</v>
+        <v>0.88525</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="C63" t="n">
-        <v>0.988776</v>
+        <v>0.372816</v>
       </c>
       <c r="D63" t="n">
-        <v>0.830653</v>
+        <v>0.907178</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C64" t="n">
-        <v>0.848091</v>
+        <v>0.431192</v>
       </c>
       <c r="D64" t="n">
-        <v>0.8675929999999999</v>
+        <v>0.895868</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="C65" t="n">
-        <v>0.648765</v>
+        <v>0.333773</v>
       </c>
       <c r="D65" t="n">
-        <v>0.853162</v>
+        <v>0.89649</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C66" t="n">
-        <v>0.525343</v>
+        <v>0.345118</v>
       </c>
       <c r="D66" t="n">
-        <v>0.871818</v>
+        <v>0.902276</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="C67" t="n">
-        <v>0.428354</v>
+        <v>0.288858</v>
       </c>
       <c r="D67" t="n">
-        <v>0.899905</v>
+        <v>0.904236</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>0.359441</v>
+        <v>0.34511</v>
       </c>
       <c r="D68" t="n">
-        <v>0.877705</v>
+        <v>0.911494</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C69" t="n">
-        <v>0.303251</v>
+        <v>0.301999</v>
       </c>
       <c r="D69" t="n">
-        <v>0.885854</v>
+        <v>0.917034</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C70" t="n">
-        <v>0.225975</v>
+        <v>0.297118</v>
       </c>
       <c r="D70" t="n">
-        <v>0.90122</v>
+        <v>0.907309</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C71" t="n">
-        <v>0.162887</v>
+        <v>0.250543</v>
       </c>
       <c r="D71" t="n">
-        <v>0.904389</v>
+        <v>0.911369</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C72" t="n">
-        <v>0.125597</v>
+        <v>0.257714</v>
       </c>
       <c r="D72" t="n">
-        <v>0.898591</v>
+        <v>0.912501</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C73" t="n">
-        <v>0.117821</v>
+        <v>0.239913</v>
       </c>
       <c r="D73" t="n">
-        <v>0.901069</v>
+        <v>0.881954</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C74" t="n">
-        <v>0.124432</v>
+        <v>0.370145</v>
       </c>
       <c r="D74" t="n">
-        <v>0.910714</v>
+        <v>0.903006</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C75" t="n">
-        <v>0.106507</v>
+        <v>0.291567</v>
       </c>
       <c r="D75" t="n">
-        <v>0.90277</v>
+        <v>0.910678</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="C76" t="n">
-        <v>0.096859</v>
+        <v>0.2399</v>
       </c>
       <c r="D76" t="n">
-        <v>0.9055260000000001</v>
+        <v>0.9146570000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C77" t="n">
-        <v>0.09576999999999999</v>
+        <v>0.21327</v>
       </c>
       <c r="D77" t="n">
-        <v>0.908752</v>
+        <v>0.909639</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="C78" t="n">
-        <v>0.100651</v>
+        <v>0.194391</v>
       </c>
       <c r="D78" t="n">
-        <v>0.913459</v>
+        <v>0.913448</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="C79" t="n">
-        <v>0.089924</v>
+        <v>0.297834</v>
       </c>
       <c r="D79" t="n">
-        <v>0.913669</v>
+        <v>0.917691</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="C80" t="n">
-        <v>0.08436299999999999</v>
+        <v>0.227969</v>
       </c>
       <c r="D80" t="n">
-        <v>0.911816</v>
+        <v>0.923198</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>PLWCE+Dice+BL               (α=13.026)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C81" t="n">
-        <v>0.093183</v>
+        <v>0.23091</v>
       </c>
       <c r="D81" t="n">
-        <v>0.912761</v>
+        <v>0.925625</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C82" t="n">
-        <v>1.618019</v>
+        <v>0.203244</v>
       </c>
       <c r="D82" t="n">
-        <v>0.805934</v>
+        <v>0.919477</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="C83" t="n">
-        <v>0.810104</v>
+        <v>0.202762</v>
       </c>
       <c r="D83" t="n">
-        <v>0.835375</v>
+        <v>0.908314</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="C84" t="n">
-        <v>0.547366</v>
+        <v>0.196588</v>
       </c>
       <c r="D84" t="n">
-        <v>0.861827</v>
+        <v>0.917941</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C85" t="n">
-        <v>0.479721</v>
+        <v>0.187403</v>
       </c>
       <c r="D85" t="n">
-        <v>0.883019</v>
+        <v>0.919227</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="C86" t="n">
-        <v>0.391816</v>
+        <v>0.180295</v>
       </c>
       <c r="D86" t="n">
-        <v>0.87121</v>
+        <v>0.892966</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C87" t="n">
-        <v>0.312411</v>
+        <v>0.185164</v>
       </c>
       <c r="D87" t="n">
-        <v>0.8895459999999999</v>
+        <v>0.919314</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="C88" t="n">
-        <v>0.280023</v>
+        <v>0.159122</v>
       </c>
       <c r="D88" t="n">
-        <v>0.9088310000000001</v>
+        <v>0.921355</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="C89" t="n">
-        <v>0.233193</v>
+        <v>0.163392</v>
       </c>
       <c r="D89" t="n">
-        <v>0.890772</v>
+        <v>0.922787</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C90" t="n">
-        <v>0.183245</v>
+        <v>0.156574</v>
       </c>
       <c r="D90" t="n">
-        <v>0.900292</v>
+        <v>0.9222089999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C91" t="n">
-        <v>0.1335</v>
+        <v>0.157717</v>
       </c>
       <c r="D91" t="n">
-        <v>0.910088</v>
+        <v>0.920743</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="C92" t="n">
-        <v>0.107385</v>
+        <v>0.148888</v>
       </c>
       <c r="D92" t="n">
-        <v>0.907331</v>
+        <v>0.92535</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="C93" t="n">
-        <v>0.082736</v>
+        <v>0.143557</v>
       </c>
       <c r="D93" t="n">
-        <v>0.911926</v>
+        <v>0.923462</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C94" t="n">
-        <v>0.081112</v>
+        <v>0.143997</v>
       </c>
       <c r="D94" t="n">
-        <v>0.9107229999999999</v>
+        <v>0.926155</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C95" t="n">
-        <v>0.070405</v>
+        <v>0.142705</v>
       </c>
       <c r="D95" t="n">
-        <v>0.912061</v>
+        <v>0.9242899999999999</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="C96" t="n">
-        <v>0.070769</v>
+        <v>0.139363</v>
       </c>
       <c r="D96" t="n">
-        <v>0.916385</v>
+        <v>0.921523</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C97" t="n">
-        <v>0.06683699999999999</v>
+        <v>0.138701</v>
       </c>
       <c r="D97" t="n">
-        <v>0.912862</v>
+        <v>0.921838</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="C98" t="n">
-        <v>0.063467</v>
+        <v>0.133419</v>
       </c>
       <c r="D98" t="n">
-        <v>0.910882</v>
+        <v>0.924749</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="C99" t="n">
-        <v>0.062148</v>
+        <v>0.140263</v>
       </c>
       <c r="D99" t="n">
-        <v>0.915582</v>
+        <v>0.920809</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="C100" t="n">
-        <v>0.062512</v>
+        <v>0.13089</v>
       </c>
       <c r="D100" t="n">
-        <v>0.915239</v>
+        <v>0.922234</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PLWCE+BL     (no Dice)       (α=3.158)</t>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
         </is>
       </c>
       <c r="B101" t="n">
+        <v>49</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.132827</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0.922221</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>50</v>
+      </c>
+      <c r="C102" t="n">
+        <v>0.12575</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0.92365</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>51</v>
+      </c>
+      <c r="C103" t="n">
+        <v>0.128747</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0.920082</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>52</v>
+      </c>
+      <c r="C104" t="n">
+        <v>0.12787</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0.922984</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>53</v>
+      </c>
+      <c r="C105" t="n">
+        <v>0.122716</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0.921923</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>54</v>
+      </c>
+      <c r="C106" t="n">
+        <v>0.123395</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0.924615</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>55</v>
+      </c>
+      <c r="C107" t="n">
+        <v>0.119274</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0.923892</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>56</v>
+      </c>
+      <c r="C108" t="n">
+        <v>0.117862</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0.921976</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice                  (α=7.105) [baseline]</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>57</v>
+      </c>
+      <c r="C109" t="n">
+        <v>0.117687</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0.923377</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="n">
+        <v>1.761306</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0.829134</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" t="n">
+        <v>1.044412</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0.845595</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>3</v>
+      </c>
+      <c r="C112" t="n">
+        <v>0.799333</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0.858663</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>4</v>
+      </c>
+      <c r="C113" t="n">
+        <v>0.64734</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0.862553</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>5</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.60451</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0.864193</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>6</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.537043</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0.895587</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>7</v>
+      </c>
+      <c r="C116" t="n">
+        <v>0.529074</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0.896161</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>8</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.474174</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.902576</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>9</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.426149</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.898957</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>10</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.414271</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.907514</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>11</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.9055260000000001</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>12</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.357529</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.912461</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>13</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.329364</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.914306</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>14</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.318131</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.910776</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>15</v>
+      </c>
+      <c r="C124" t="n">
+        <v>0.2915</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.884067</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.347067</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.901964</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>17</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.909085</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>18</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.319378</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.910498</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>19</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.282012</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.915866</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
         <v>20</v>
       </c>
-      <c r="C101" t="n">
-        <v>0.060166</v>
-      </c>
-      <c r="D101" t="n">
-        <v>0.916678</v>
+      <c r="C129" t="n">
+        <v>0.229121</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.916189</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>21</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.269482</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.8963140000000001</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>22</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.211274</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.923381</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>23</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.224333</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.909809</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>24</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.247666</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.9178190000000001</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>25</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.182852</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.910103</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>26</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.185135</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.924357</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>27</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.171768</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.915681</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>28</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.173535</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.923477</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>29</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.15692</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.925448</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>30</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.1446</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.928166</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>31</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.148401</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.925102</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>32</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.134</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.919983</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>33</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.131554</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.91464</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>34</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.132032</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.915417</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>35</v>
+      </c>
+      <c r="C144" t="n">
+        <v>0.137366</v>
+      </c>
+      <c r="D144" t="n">
+        <v>0.879578</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>36</v>
+      </c>
+      <c r="C145" t="n">
+        <v>0.149342</v>
+      </c>
+      <c r="D145" t="n">
+        <v>0.919498</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>37</v>
+      </c>
+      <c r="C146" t="n">
+        <v>0.127879</v>
+      </c>
+      <c r="D146" t="n">
+        <v>0.914091</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>38</v>
+      </c>
+      <c r="C147" t="n">
+        <v>0.120379</v>
+      </c>
+      <c r="D147" t="n">
+        <v>0.9194059999999999</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>39</v>
+      </c>
+      <c r="C148" t="n">
+        <v>0.126098</v>
+      </c>
+      <c r="D148" t="n">
+        <v>0.913702</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>40</v>
+      </c>
+      <c r="C149" t="n">
+        <v>0.112985</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0.915459</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>41</v>
+      </c>
+      <c r="C150" t="n">
+        <v>0.113272</v>
+      </c>
+      <c r="D150" t="n">
+        <v>0.92153</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>42</v>
+      </c>
+      <c r="C151" t="n">
+        <v>0.103606</v>
+      </c>
+      <c r="D151" t="n">
+        <v>0.921474</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>43</v>
+      </c>
+      <c r="C152" t="n">
+        <v>0.09709</v>
+      </c>
+      <c r="D152" t="n">
+        <v>0.9172940000000001</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>44</v>
+      </c>
+      <c r="C153" t="n">
+        <v>0.095896</v>
+      </c>
+      <c r="D153" t="n">
+        <v>0.916413</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>CE+Dice+BL                  [literature]</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>45</v>
+      </c>
+      <c r="C154" t="n">
+        <v>0.091072</v>
+      </c>
+      <c r="D154" t="n">
+        <v>0.917643</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1.746673</v>
+      </c>
+      <c r="D155" t="n">
+        <v>0.827161</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>2</v>
+      </c>
+      <c r="C156" t="n">
+        <v>1.028223</v>
+      </c>
+      <c r="D156" t="n">
+        <v>0.864465</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>3</v>
+      </c>
+      <c r="C157" t="n">
+        <v>0.7987649999999999</v>
+      </c>
+      <c r="D157" t="n">
+        <v>0.875597</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>4</v>
+      </c>
+      <c r="C158" t="n">
+        <v>0.700654</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.861005</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>5</v>
+      </c>
+      <c r="C159" t="n">
+        <v>0.621144</v>
+      </c>
+      <c r="D159" t="n">
+        <v>0.90171</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>6</v>
+      </c>
+      <c r="C160" t="n">
+        <v>0.596339</v>
+      </c>
+      <c r="D160" t="n">
+        <v>0.892947</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>7</v>
+      </c>
+      <c r="C161" t="n">
+        <v>0.535036</v>
+      </c>
+      <c r="D161" t="n">
+        <v>0.901536</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>8</v>
+      </c>
+      <c r="C162" t="n">
+        <v>0.448142</v>
+      </c>
+      <c r="D162" t="n">
+        <v>0.910542</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>9</v>
+      </c>
+      <c r="C163" t="n">
+        <v>0.444125</v>
+      </c>
+      <c r="D163" t="n">
+        <v>0.8976730000000001</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>10</v>
+      </c>
+      <c r="C164" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.899802</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>11</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.395508</v>
+      </c>
+      <c r="D165" t="n">
+        <v>0.910797</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>12</v>
+      </c>
+      <c r="C166" t="n">
+        <v>0.397504</v>
+      </c>
+      <c r="D166" t="n">
+        <v>0.90329</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>13</v>
+      </c>
+      <c r="C167" t="n">
+        <v>0.357186</v>
+      </c>
+      <c r="D167" t="n">
+        <v>0.900932</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>14</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.332083</v>
+      </c>
+      <c r="D168" t="n">
+        <v>0.910922</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>15</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="D169" t="n">
+        <v>0.914534</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>0.306752</v>
+      </c>
+      <c r="D170" t="n">
+        <v>0.921291</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>17</v>
+      </c>
+      <c r="C171" t="n">
+        <v>0.314258</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.914312</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>18</v>
+      </c>
+      <c r="C172" t="n">
+        <v>0.259764</v>
+      </c>
+      <c r="D172" t="n">
+        <v>0.90278</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B173" t="n">
+        <v>19</v>
+      </c>
+      <c r="C173" t="n">
+        <v>0.266982</v>
+      </c>
+      <c r="D173" t="n">
+        <v>0.9238499999999999</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B174" t="n">
+        <v>20</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.242419</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.920033</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B175" t="n">
+        <v>21</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.226689</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.917179</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B176" t="n">
+        <v>22</v>
+      </c>
+      <c r="C176" t="n">
+        <v>0.303888</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.885132</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B177" t="n">
+        <v>23</v>
+      </c>
+      <c r="C177" t="n">
+        <v>0.278262</v>
+      </c>
+      <c r="D177" t="n">
+        <v>0.903475</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B178" t="n">
+        <v>24</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.249281</v>
+      </c>
+      <c r="D178" t="n">
+        <v>0.917859</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B179" t="n">
+        <v>25</v>
+      </c>
+      <c r="C179" t="n">
+        <v>0.213167</v>
+      </c>
+      <c r="D179" t="n">
+        <v>0.911581</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B180" t="n">
+        <v>26</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.205456</v>
+      </c>
+      <c r="D180" t="n">
+        <v>0.912818</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B181" t="n">
+        <v>27</v>
+      </c>
+      <c r="C181" t="n">
+        <v>0.182845</v>
+      </c>
+      <c r="D181" t="n">
+        <v>0.91792</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B182" t="n">
+        <v>28</v>
+      </c>
+      <c r="C182" t="n">
+        <v>0.160286</v>
+      </c>
+      <c r="D182" t="n">
+        <v>0.9129699999999999</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B183" t="n">
+        <v>29</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.175184</v>
+      </c>
+      <c r="D183" t="n">
+        <v>0.908737</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B184" t="n">
+        <v>30</v>
+      </c>
+      <c r="C184" t="n">
+        <v>0.180838</v>
+      </c>
+      <c r="D184" t="n">
+        <v>0.923491</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B185" t="n">
+        <v>31</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.161764</v>
+      </c>
+      <c r="D185" t="n">
+        <v>0.915114</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B186" t="n">
+        <v>32</v>
+      </c>
+      <c r="C186" t="n">
+        <v>0.147985</v>
+      </c>
+      <c r="D186" t="n">
+        <v>0.926991</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B187" t="n">
+        <v>33</v>
+      </c>
+      <c r="C187" t="n">
+        <v>0.153438</v>
+      </c>
+      <c r="D187" t="n">
+        <v>0.878078</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>34</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0.231455</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0.923211</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B189" t="n">
+        <v>35</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.169564</v>
+      </c>
+      <c r="D189" t="n">
+        <v>0.917848</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B190" t="n">
+        <v>36</v>
+      </c>
+      <c r="C190" t="n">
+        <v>0.137742</v>
+      </c>
+      <c r="D190" t="n">
+        <v>0.91819</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B191" t="n">
+        <v>37</v>
+      </c>
+      <c r="C191" t="n">
+        <v>0.141144</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.921721</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B192" t="n">
+        <v>38</v>
+      </c>
+      <c r="C192" t="n">
+        <v>0.1257</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.921367</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B193" t="n">
+        <v>39</v>
+      </c>
+      <c r="C193" t="n">
+        <v>0.129695</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.923023</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B194" t="n">
+        <v>40</v>
+      </c>
+      <c r="C194" t="n">
+        <v>0.117152</v>
+      </c>
+      <c r="D194" t="n">
+        <v>0.928845</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B195" t="n">
+        <v>41</v>
+      </c>
+      <c r="C195" t="n">
+        <v>0.11582</v>
+      </c>
+      <c r="D195" t="n">
+        <v>0.927152</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B196" t="n">
+        <v>42</v>
+      </c>
+      <c r="C196" t="n">
+        <v>0.114838</v>
+      </c>
+      <c r="D196" t="n">
+        <v>0.921843</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B197" t="n">
+        <v>43</v>
+      </c>
+      <c r="C197" t="n">
+        <v>0.10907</v>
+      </c>
+      <c r="D197" t="n">
+        <v>0.921881</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B198" t="n">
+        <v>44</v>
+      </c>
+      <c r="C198" t="n">
+        <v>0.103504</v>
+      </c>
+      <c r="D198" t="n">
+        <v>0.926222</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B199" t="n">
+        <v>45</v>
+      </c>
+      <c r="C199" t="n">
+        <v>0.099271</v>
+      </c>
+      <c r="D199" t="n">
+        <v>0.925072</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B200" t="n">
+        <v>46</v>
+      </c>
+      <c r="C200" t="n">
+        <v>0.096636</v>
+      </c>
+      <c r="D200" t="n">
+        <v>0.926739</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B201" t="n">
+        <v>47</v>
+      </c>
+      <c r="C201" t="n">
+        <v>0.097217</v>
+      </c>
+      <c r="D201" t="n">
+        <v>0.927828</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B202" t="n">
+        <v>48</v>
+      </c>
+      <c r="C202" t="n">
+        <v>0.09515999999999999</v>
+      </c>
+      <c r="D202" t="n">
+        <v>0.926718</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B203" t="n">
+        <v>49</v>
+      </c>
+      <c r="C203" t="n">
+        <v>0.089847</v>
+      </c>
+      <c r="D203" t="n">
+        <v>0.92658</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B204" t="n">
+        <v>50</v>
+      </c>
+      <c r="C204" t="n">
+        <v>0.08368399999999999</v>
+      </c>
+      <c r="D204" t="n">
+        <v>0.926399</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B205" t="n">
+        <v>51</v>
+      </c>
+      <c r="C205" t="n">
+        <v>0.08645</v>
+      </c>
+      <c r="D205" t="n">
+        <v>0.925656</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B206" t="n">
+        <v>52</v>
+      </c>
+      <c r="C206" t="n">
+        <v>0.081223</v>
+      </c>
+      <c r="D206" t="n">
+        <v>0.923884</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B207" t="n">
+        <v>53</v>
+      </c>
+      <c r="C207" t="n">
+        <v>0.08198999999999999</v>
+      </c>
+      <c r="D207" t="n">
+        <v>0.922176</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B208" t="n">
+        <v>54</v>
+      </c>
+      <c r="C208" t="n">
+        <v>0.078435</v>
+      </c>
+      <c r="D208" t="n">
+        <v>0.926538</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>PLWCE+Dice+BL               (α=7.105)</t>
+        </is>
+      </c>
+      <c r="B209" t="n">
+        <v>55</v>
+      </c>
+      <c r="C209" t="n">
+        <v>0.08321000000000001</v>
+      </c>
+      <c r="D209" t="n">
+        <v>0.926203</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="n">
+        <v>1.610838</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.747254</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B211" t="n">
+        <v>2</v>
+      </c>
+      <c r="C211" t="n">
+        <v>0.824767</v>
+      </c>
+      <c r="D211" t="n">
+        <v>0.831935</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B212" t="n">
+        <v>3</v>
+      </c>
+      <c r="C212" t="n">
+        <v>0.657901</v>
+      </c>
+      <c r="D212" t="n">
+        <v>0.857943</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B213" t="n">
+        <v>4</v>
+      </c>
+      <c r="C213" t="n">
+        <v>0.575912</v>
+      </c>
+      <c r="D213" t="n">
+        <v>0.885839</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B214" t="n">
+        <v>5</v>
+      </c>
+      <c r="C214" t="n">
+        <v>0.506642</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.86765</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B215" t="n">
+        <v>6</v>
+      </c>
+      <c r="C215" t="n">
+        <v>0.455272</v>
+      </c>
+      <c r="D215" t="n">
+        <v>0.863971</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>7</v>
+      </c>
+      <c r="C216" t="n">
+        <v>0.403414</v>
+      </c>
+      <c r="D216" t="n">
+        <v>0.868527</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>8</v>
+      </c>
+      <c r="C217" t="n">
+        <v>0.398685</v>
+      </c>
+      <c r="D217" t="n">
+        <v>0.89662</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>9</v>
+      </c>
+      <c r="C218" t="n">
+        <v>0.333923</v>
+      </c>
+      <c r="D218" t="n">
+        <v>0.901729</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>10</v>
+      </c>
+      <c r="C219" t="n">
+        <v>0.317164</v>
+      </c>
+      <c r="D219" t="n">
+        <v>0.884178</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>11</v>
+      </c>
+      <c r="C220" t="n">
+        <v>0.280864</v>
+      </c>
+      <c r="D220" t="n">
+        <v>0.884736</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>12</v>
+      </c>
+      <c r="C221" t="n">
+        <v>0.2671</v>
+      </c>
+      <c r="D221" t="n">
+        <v>0.899517</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>13</v>
+      </c>
+      <c r="C222" t="n">
+        <v>0.283045</v>
+      </c>
+      <c r="D222" t="n">
+        <v>0.897822</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>14</v>
+      </c>
+      <c r="C223" t="n">
+        <v>0.239503</v>
+      </c>
+      <c r="D223" t="n">
+        <v>0.889818</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>15</v>
+      </c>
+      <c r="C224" t="n">
+        <v>0.238337</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.905964</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B225" t="n">
+        <v>16</v>
+      </c>
+      <c r="C225" t="n">
+        <v>0.234537</v>
+      </c>
+      <c r="D225" t="n">
+        <v>0.891201</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B226" t="n">
+        <v>17</v>
+      </c>
+      <c r="C226" t="n">
+        <v>0.268722</v>
+      </c>
+      <c r="D226" t="n">
+        <v>0.900622</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B227" t="n">
+        <v>18</v>
+      </c>
+      <c r="C227" t="n">
+        <v>0.212342</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.888104</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B228" t="n">
+        <v>19</v>
+      </c>
+      <c r="C228" t="n">
+        <v>0.192144</v>
+      </c>
+      <c r="D228" t="n">
+        <v>0.890879</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B229" t="n">
+        <v>20</v>
+      </c>
+      <c r="C229" t="n">
+        <v>0.200775</v>
+      </c>
+      <c r="D229" t="n">
+        <v>0.867321</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B230" t="n">
+        <v>21</v>
+      </c>
+      <c r="C230" t="n">
+        <v>0.19745</v>
+      </c>
+      <c r="D230" t="n">
+        <v>0.907201</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B231" t="n">
+        <v>22</v>
+      </c>
+      <c r="C231" t="n">
+        <v>0.175733</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.906115</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B232" t="n">
+        <v>23</v>
+      </c>
+      <c r="C232" t="n">
+        <v>0.165619</v>
+      </c>
+      <c r="D232" t="n">
+        <v>0.915845</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B233" t="n">
+        <v>24</v>
+      </c>
+      <c r="C233" t="n">
+        <v>0.143604</v>
+      </c>
+      <c r="D233" t="n">
+        <v>0.90567</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B234" t="n">
+        <v>25</v>
+      </c>
+      <c r="C234" t="n">
+        <v>0.132688</v>
+      </c>
+      <c r="D234" t="n">
+        <v>0.915301</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B235" t="n">
+        <v>26</v>
+      </c>
+      <c r="C235" t="n">
+        <v>0.172985</v>
+      </c>
+      <c r="D235" t="n">
+        <v>0.884145</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B236" t="n">
+        <v>27</v>
+      </c>
+      <c r="C236" t="n">
+        <v>0.276891</v>
+      </c>
+      <c r="D236" t="n">
+        <v>0.902126</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B237" t="n">
+        <v>28</v>
+      </c>
+      <c r="C237" t="n">
+        <v>0.170709</v>
+      </c>
+      <c r="D237" t="n">
+        <v>0.906021</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B238" t="n">
+        <v>29</v>
+      </c>
+      <c r="C238" t="n">
+        <v>0.150315</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.910133</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B239" t="n">
+        <v>30</v>
+      </c>
+      <c r="C239" t="n">
+        <v>0.127876</v>
+      </c>
+      <c r="D239" t="n">
+        <v>0.921148</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B240" t="n">
+        <v>31</v>
+      </c>
+      <c r="C240" t="n">
+        <v>0.105212</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.920993</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B241" t="n">
+        <v>32</v>
+      </c>
+      <c r="C241" t="n">
+        <v>0.109614</v>
+      </c>
+      <c r="D241" t="n">
+        <v>0.92057</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B242" t="n">
+        <v>33</v>
+      </c>
+      <c r="C242" t="n">
+        <v>0.101508</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.922992</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B243" t="n">
+        <v>34</v>
+      </c>
+      <c r="C243" t="n">
+        <v>0.090486</v>
+      </c>
+      <c r="D243" t="n">
+        <v>0.922897</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B244" t="n">
+        <v>35</v>
+      </c>
+      <c r="C244" t="n">
+        <v>0.09135799999999999</v>
+      </c>
+      <c r="D244" t="n">
+        <v>0.91538</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>36</v>
+      </c>
+      <c r="C245" t="n">
+        <v>0.08647100000000001</v>
+      </c>
+      <c r="D245" t="n">
+        <v>0.912312</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>37</v>
+      </c>
+      <c r="C246" t="n">
+        <v>0.083895</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.91565</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>38</v>
+      </c>
+      <c r="C247" t="n">
+        <v>0.07473100000000001</v>
+      </c>
+      <c r="D247" t="n">
+        <v>0.921162</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>39</v>
+      </c>
+      <c r="C248" t="n">
+        <v>0.071411</v>
+      </c>
+      <c r="D248" t="n">
+        <v>0.921389</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>40</v>
+      </c>
+      <c r="C249" t="n">
+        <v>0.06983</v>
+      </c>
+      <c r="D249" t="n">
+        <v>0.923358</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B250" t="n">
+        <v>41</v>
+      </c>
+      <c r="C250" t="n">
+        <v>0.063766</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.920753</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B251" t="n">
+        <v>42</v>
+      </c>
+      <c r="C251" t="n">
+        <v>0.06367299999999999</v>
+      </c>
+      <c r="D251" t="n">
+        <v>0.921507</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B252" t="n">
+        <v>43</v>
+      </c>
+      <c r="C252" t="n">
+        <v>0.059418</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.921404</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B253" t="n">
+        <v>44</v>
+      </c>
+      <c r="C253" t="n">
+        <v>0.061048</v>
+      </c>
+      <c r="D253" t="n">
+        <v>0.921015</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B254" t="n">
+        <v>45</v>
+      </c>
+      <c r="C254" t="n">
+        <v>0.060659</v>
+      </c>
+      <c r="D254" t="n">
+        <v>0.919903</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B255" t="n">
+        <v>46</v>
+      </c>
+      <c r="C255" t="n">
+        <v>0.055406</v>
+      </c>
+      <c r="D255" t="n">
+        <v>0.918295</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>47</v>
+      </c>
+      <c r="C256" t="n">
+        <v>0.052015</v>
+      </c>
+      <c r="D256" t="n">
+        <v>0.9221240000000001</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>48</v>
+      </c>
+      <c r="C257" t="n">
+        <v>0.050476</v>
+      </c>
+      <c r="D257" t="n">
+        <v>0.91939</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>49</v>
+      </c>
+      <c r="C258" t="n">
+        <v>0.043359</v>
+      </c>
+      <c r="D258" t="n">
+        <v>0.922505</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>50</v>
+      </c>
+      <c r="C259" t="n">
+        <v>0.042609</v>
+      </c>
+      <c r="D259" t="n">
+        <v>0.921578</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>51</v>
+      </c>
+      <c r="C260" t="n">
+        <v>0.040105</v>
+      </c>
+      <c r="D260" t="n">
+        <v>0.923245</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B261" t="n">
+        <v>52</v>
+      </c>
+      <c r="C261" t="n">
+        <v>0.037905</v>
+      </c>
+      <c r="D261" t="n">
+        <v>0.923908</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>53</v>
+      </c>
+      <c r="C262" t="n">
+        <v>0.03469</v>
+      </c>
+      <c r="D262" t="n">
+        <v>0.9228460000000001</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>54</v>
+      </c>
+      <c r="C263" t="n">
+        <v>0.033715</v>
+      </c>
+      <c r="D263" t="n">
+        <v>0.923103</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>55</v>
+      </c>
+      <c r="C264" t="n">
+        <v>0.032969</v>
+      </c>
+      <c r="D264" t="n">
+        <v>0.92625</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>56</v>
+      </c>
+      <c r="C265" t="n">
+        <v>0.030882</v>
+      </c>
+      <c r="D265" t="n">
+        <v>0.92295</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>57</v>
+      </c>
+      <c r="C266" t="n">
+        <v>0.026515</v>
+      </c>
+      <c r="D266" t="n">
+        <v>0.923603</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>58</v>
+      </c>
+      <c r="C267" t="n">
+        <v>0.025175</v>
+      </c>
+      <c r="D267" t="n">
+        <v>0.922393</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>59</v>
+      </c>
+      <c r="C268" t="n">
+        <v>0.022431</v>
+      </c>
+      <c r="D268" t="n">
+        <v>0.922486</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>60</v>
+      </c>
+      <c r="C269" t="n">
+        <v>0.01996</v>
+      </c>
+      <c r="D269" t="n">
+        <v>0.926007</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>61</v>
+      </c>
+      <c r="C270" t="n">
+        <v>0.019853</v>
+      </c>
+      <c r="D270" t="n">
+        <v>0.925557</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>62</v>
+      </c>
+      <c r="C271" t="n">
+        <v>0.0185</v>
+      </c>
+      <c r="D271" t="n">
+        <v>0.924717</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>63</v>
+      </c>
+      <c r="C272" t="n">
+        <v>0.016347</v>
+      </c>
+      <c r="D272" t="n">
+        <v>0.92341</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>64</v>
+      </c>
+      <c r="C273" t="n">
+        <v>0.012762</v>
+      </c>
+      <c r="D273" t="n">
+        <v>0.926219</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>65</v>
+      </c>
+      <c r="C274" t="n">
+        <v>0.011363</v>
+      </c>
+      <c r="D274" t="n">
+        <v>0.92394</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>66</v>
+      </c>
+      <c r="C275" t="n">
+        <v>0.009723000000000001</v>
+      </c>
+      <c r="D275" t="n">
+        <v>0.926098</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>67</v>
+      </c>
+      <c r="C276" t="n">
+        <v>0.009436999999999999</v>
+      </c>
+      <c r="D276" t="n">
+        <v>0.926333</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>68</v>
+      </c>
+      <c r="C277" t="n">
+        <v>0.008574</v>
+      </c>
+      <c r="D277" t="n">
+        <v>0.92594</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B278" t="n">
+        <v>69</v>
+      </c>
+      <c r="C278" t="n">
+        <v>0.006607</v>
+      </c>
+      <c r="D278" t="n">
+        <v>0.925809</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B279" t="n">
+        <v>70</v>
+      </c>
+      <c r="C279" t="n">
+        <v>0.003767</v>
+      </c>
+      <c r="D279" t="n">
+        <v>0.924708</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B280" t="n">
+        <v>71</v>
+      </c>
+      <c r="C280" t="n">
+        <v>0.003092</v>
+      </c>
+      <c r="D280" t="n">
+        <v>0.924512</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B281" t="n">
+        <v>72</v>
+      </c>
+      <c r="C281" t="n">
+        <v>0.000842</v>
+      </c>
+      <c r="D281" t="n">
+        <v>0.925683</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B282" t="n">
+        <v>73</v>
+      </c>
+      <c r="C282" t="n">
+        <v>-0.000752</v>
+      </c>
+      <c r="D282" t="n">
+        <v>0.925505</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B283" t="n">
+        <v>74</v>
+      </c>
+      <c r="C283" t="n">
+        <v>-0.001709</v>
+      </c>
+      <c r="D283" t="n">
+        <v>0.925988</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>PLWCE+BL     (no Dice)       (α=2.500)</t>
+        </is>
+      </c>
+      <c r="B284" t="n">
+        <v>75</v>
+      </c>
+      <c r="C284" t="n">
+        <v>-0.004167</v>
+      </c>
+      <c r="D284" t="n">
+        <v>0.924934</v>
       </c>
     </row>
   </sheetData>
